--- a/Result/profitability/4931.xlsx
+++ b/Result/profitability/4931.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM54"/>
+  <dimension ref="A1:AM55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>5.6</v>
       </c>
       <c r="M2" t="n">
-        <v>1.4825</v>
+        <v>1.65</v>
       </c>
       <c r="N2" t="n">
-        <v>19.98</v>
+        <v>20.19</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>4.98</v>
       </c>
       <c r="M3" t="n">
-        <v>1.9975</v>
+        <v>2.17375</v>
       </c>
       <c r="N3" t="n">
-        <v>18.06125</v>
+        <v>17.63125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.18</v>
       </c>
       <c r="M4" t="n">
-        <v>2.04625</v>
+        <v>2.1475</v>
       </c>
       <c r="N4" t="n">
-        <v>15.695</v>
+        <v>15.18375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>2.63</v>
       </c>
       <c r="M5" t="n">
-        <v>2.20125</v>
+        <v>2.545</v>
       </c>
       <c r="N5" t="n">
-        <v>13.4225</v>
+        <v>15.20375</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>98.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>2.37125</v>
+        <v>2.5575</v>
       </c>
       <c r="N6" t="n">
-        <v>13.2225</v>
+        <v>13.70625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.03</v>
       </c>
       <c r="M7" t="n">
-        <v>2.27875</v>
+        <v>2.35625</v>
       </c>
       <c r="N7" t="n">
-        <v>11.6975</v>
+        <v>11.33</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -7290,6 +7290,133 @@
       </c>
       <c r="AM54" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>4931</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>1113</v>
+      </c>
+      <c r="D55" t="n">
+        <v>854</v>
+      </c>
+      <c r="E55" t="n">
+        <v>260</v>
+      </c>
+      <c r="F55" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="G55" t="n">
+        <v>168</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>15.07%</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>12</v>
+      </c>
+      <c r="J55" t="n">
+        <v>180</v>
+      </c>
+      <c r="K55" t="n">
+        <v>145</v>
+      </c>
+      <c r="L55" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1.0575</v>
+      </c>
+      <c r="N55" t="n">
+        <v>22.0075</v>
+      </c>
+      <c r="O55" t="n">
+        <v>1</v>
+      </c>
+      <c r="P55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>1</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0.7200000000000002</v>
+      </c>
+      <c r="X55" t="n">
+        <v>0.4864864864864866</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>0.05661231884057982</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>1.569383259911894</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK55" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
